--- a/research/graceyou-comparison/candidates.xlsx
+++ b/research/graceyou-comparison/candidates.xlsx
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>candidates/b570184.md</t>
+          <t>candidates/b579965.md</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>candidates/b813367.md</t>
+          <t>candidates/b21d426.md</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>candidates/b389077.md</t>
+          <t>candidates/ba1f1a7.md</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>candidates/b780125.md</t>
+          <t>candidates/b4caf1d.md</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>candidates/b426622.md</t>
+          <t>candidates/be09548.md</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>candidates/b615920.md</t>
+          <t>candidates/b6d2f2a.md</t>
         </is>
       </c>
     </row>
@@ -20090,7 +20090,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>모던 데일리 엘레강스 페미닌 로맨틱 소재중시 클래식</t>
+          <t>로맨틱 소재중시 데일리 클래식 엘레강스 모던 페미닌</t>
         </is>
       </c>
     </row>
@@ -20121,12 +20121,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>공식몰 상의(74개) 정가 Q1·중앙·Q3</t>
+          <t>공식몰 상의(55개, 색 합침) 판매가 Q1·중앙·Q3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>114,250 · 158,000 · 226,750</t>
+          <t>101,500 · 153,000 · 218,000</t>
         </is>
       </c>
     </row>

--- a/research/graceyou-comparison/candidates.xlsx
+++ b/research/graceyou-comparison/candidates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="후보풀" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="근거기사" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="그레이스유 기준" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="산식·역할" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="후보풀" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="근거기사" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그레이스유 기준" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="산식·역할" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'후보풀'!$A$1:$AE$103</definedName>
@@ -643,12 +643,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>후보</t>
+          <t>추천</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>가격·무드 모두 근접</t>
+          <t>경쟁사 추천(우아함 대체재)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -731,7 +731,11 @@
         <v>109224</v>
       </c>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>그레이스유 경쟁사 추천(2026-10-29, Claude 기준): 정가 중앙 -13%·클래식 페미닌 무드·W컨셉 입점·그레이스유와 함께 기사 언급. 사용자 미확정.</t>
+        </is>
+      </c>
       <c r="AE2" t="inlineStr">
         <is>
           <t>candidates/lamerei.md</t>
@@ -1296,12 +1300,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>후보</t>
+          <t>추천</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>가격·무드 모두 근접</t>
+          <t>경쟁사 추천(우아함 대체재)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1374,7 +1378,11 @@
         <v>113288</v>
       </c>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>그레이스유 경쟁사 추천(2026-10-29, Claude 기준): 정가 중앙 +3%·엘레강스 클래식 페미닌 무드·W컨셉 입점. W컨셉 중앙 할인 66%라 결제가는 크게 낮다. 사용자 미확정.</t>
+        </is>
+      </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>candidates/besti-belli.md</t>
@@ -3023,12 +3031,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>후보</t>
+          <t>추천</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>가격 근접·무드 다름</t>
+          <t>경쟁사 추천(우아함 대체재)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3101,7 +3109,11 @@
         <v>105721</v>
       </c>
       <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>그레이스유 경쟁사 추천(2026-10-29, Claude 기준): 정가 중앙 -23%·엘레강스 클래식 무드·W컨셉 입점(중앙 할인 13%, 그레이스유와 같은 수준)·그레이스유와 함께 퀸잇 디자이너 전문관 기사 언급. 사용자 미확정.</t>
+        </is>
+      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>candidates/voyonn.md</t>
@@ -20090,7 +20102,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>로맨틱 소재중시 데일리 클래식 엘레강스 모던 페미닌</t>
+          <t>데일리 엘레강스 클래식 페미닌 모던 소재중시 로맨틱</t>
         </is>
       </c>
     </row>

--- a/research/graceyou-comparison/candidates.xlsx
+++ b/research/graceyou-comparison/candidates.xlsx
@@ -758,12 +758,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>후보</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>가격·무드 모두 근접</t>
+          <t>직접 경쟁(확정)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -845,7 +845,11 @@
           <t>https://orr.store</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>기획서 §10-23(2026-10-29)에서 쉬즈미스 대신 핵심 비교군에 추가. 테일러링·소재·드레시한 상의 비교 대상. 기준선 수집은 monitor/.</t>
+        </is>
+      </c>
       <c r="AE3" t="inlineStr">
         <is>
           <t>candidates/orr.md</t>
@@ -969,12 +973,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>후보</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>직접 경쟁(확정)</t>
+          <t>가격·무드 모두 근접</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1059,7 +1063,11 @@
           <t>https://www.idfmall.co.kr</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>10-29 처음 확정 4곳에 들었으나 기획서 §10-23에서 핵심 비교군에서 제외(오르로 교체). 상의 한 장 표(onepager)에는 그대로 남아 있다.</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>candidates/shesmiss.md</t>
@@ -20102,7 +20110,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>데일리 엘레강스 클래식 페미닌 모던 소재중시 로맨틱</t>
+          <t>데일리 클래식 엘레강스 모던 페미닌 로맨틱 소재중시</t>
         </is>
       </c>
     </row>

--- a/research/graceyou-comparison/candidates.xlsx
+++ b/research/graceyou-comparison/candidates.xlsx
@@ -20110,7 +20110,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>데일리 클래식 엘레강스 모던 페미닌 로맨틱 소재중시</t>
+          <t>소재중시 모던 로맨틱 클래식 엘레강스 페미닌 데일리</t>
         </is>
       </c>
     </row>
